--- a/test/fixtures/xlsx/multi-target/multi-target.xlsx
+++ b/test/fixtures/xlsx/multi-target/multi-target.xlsx
@@ -8,12 +8,13 @@
   <sheets>
     <sheet name="Catalogues" sheetId="1" r:id="rId3"/>
     <sheet name="Holders" sheetId="2" r:id="rId4"/>
+    <sheet name="Groups" sheetId="3" r:id="rId5"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="93">
   <si>
     <t xml:space="preserve">~~table:Weapon~~</t>
   </si>
@@ -196,6 +197,102 @@
   </si>
   <si>
     <t xml:space="preserve">3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~~table:Loadout~~</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A record array whose member reaches several tables.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slot1.Pick</t>
+  </si>
+  <si>
+    <t xml:space="preserve">element 1 - two targets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slot1.Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">element 1 - an ordinary member</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slot2.Pick</t>
+  </si>
+  <si>
+    <t xml:space="preserve">element 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slot2.Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~~table:Fitting~~</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One record - no element number at all - whose member reaches several.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Main.Pick</t>
+  </si>
+  <si>
+    <t xml:space="preserve">the member, in a record of one</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Main.Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">an ordinary member beside it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">padding, so every table is one width</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pad2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~~table:Rack~~</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One record whose members are arrays, one of them reaching several.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slots.Pick1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">element 1 of the member</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slots.Pick2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">element 2 of the member</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slots.Count1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">element 1 beside it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slots.Count2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">element 2 beside it</t>
   </si>
 </sst>
 </file>
@@ -765,4 +862,365 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="B2:V10"/>
+  <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="2">
+      <c r="B2" t="s">
+        <v>61</v>
+      </c>
+      <c r="J2" t="s">
+        <v>71</v>
+      </c>
+      <c r="R2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" t="s">
+        <v>62</v>
+      </c>
+      <c r="J3" t="s">
+        <v>72</v>
+      </c>
+      <c r="R3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E4" t="s">
+        <v>67</v>
+      </c>
+      <c r="F4" t="s">
+        <v>69</v>
+      </c>
+      <c r="J4" t="s">
+        <v>2</v>
+      </c>
+      <c r="K4" t="s">
+        <v>73</v>
+      </c>
+      <c r="L4" t="s">
+        <v>75</v>
+      </c>
+      <c r="M4" t="s">
+        <v>77</v>
+      </c>
+      <c r="N4" t="s">
+        <v>79</v>
+      </c>
+      <c r="R4" t="s">
+        <v>2</v>
+      </c>
+      <c r="S4" t="s">
+        <v>85</v>
+      </c>
+      <c r="T4" t="s">
+        <v>87</v>
+      </c>
+      <c r="U4" t="s">
+        <v>89</v>
+      </c>
+      <c r="V4" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D5" t="s">
+        <v>66</v>
+      </c>
+      <c r="E5" t="s">
+        <v>68</v>
+      </c>
+      <c r="F5" t="s">
+        <v>68</v>
+      </c>
+      <c r="J5" t="s">
+        <v>43</v>
+      </c>
+      <c r="K5" t="s">
+        <v>74</v>
+      </c>
+      <c r="L5" t="s">
+        <v>76</v>
+      </c>
+      <c r="M5" t="s">
+        <v>78</v>
+      </c>
+      <c r="N5" t="s">
+        <v>78</v>
+      </c>
+      <c r="R5" t="s">
+        <v>43</v>
+      </c>
+      <c r="S5" t="s">
+        <v>86</v>
+      </c>
+      <c r="T5" t="s">
+        <v>88</v>
+      </c>
+      <c r="U5" t="s">
+        <v>90</v>
+      </c>
+      <c r="V5" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" t="s">
+        <v>46</v>
+      </c>
+      <c r="D6" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" t="s">
+        <v>46</v>
+      </c>
+      <c r="F6" t="s">
+        <v>4</v>
+      </c>
+      <c r="J6" t="s">
+        <v>4</v>
+      </c>
+      <c r="K6" t="s">
+        <v>46</v>
+      </c>
+      <c r="L6" t="s">
+        <v>4</v>
+      </c>
+      <c r="M6" t="s">
+        <v>4</v>
+      </c>
+      <c r="N6" t="s">
+        <v>4</v>
+      </c>
+      <c r="R6" t="s">
+        <v>4</v>
+      </c>
+      <c r="S6" t="s">
+        <v>46</v>
+      </c>
+      <c r="T6" t="s">
+        <v>46</v>
+      </c>
+      <c r="U6" t="s">
+        <v>4</v>
+      </c>
+      <c r="V6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F7" t="s">
+        <v>5</v>
+      </c>
+      <c r="J7" t="s">
+        <v>5</v>
+      </c>
+      <c r="K7" t="s">
+        <v>47</v>
+      </c>
+      <c r="L7" t="s">
+        <v>5</v>
+      </c>
+      <c r="M7" t="s">
+        <v>5</v>
+      </c>
+      <c r="N7" t="s">
+        <v>5</v>
+      </c>
+      <c r="R7" t="s">
+        <v>5</v>
+      </c>
+      <c r="S7" t="s">
+        <v>47</v>
+      </c>
+      <c r="T7" t="s">
+        <v>47</v>
+      </c>
+      <c r="U7" t="s">
+        <v>5</v>
+      </c>
+      <c r="V7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E8" t="s">
+        <v>6</v>
+      </c>
+      <c r="F8" t="s">
+        <v>6</v>
+      </c>
+      <c r="J8" t="s">
+        <v>6</v>
+      </c>
+      <c r="K8" t="s">
+        <v>6</v>
+      </c>
+      <c r="L8" t="s">
+        <v>6</v>
+      </c>
+      <c r="M8" t="s">
+        <v>6</v>
+      </c>
+      <c r="N8" t="s">
+        <v>6</v>
+      </c>
+      <c r="R8" t="s">
+        <v>6</v>
+      </c>
+      <c r="S8" t="s">
+        <v>6</v>
+      </c>
+      <c r="T8" t="s">
+        <v>6</v>
+      </c>
+      <c r="U8" t="s">
+        <v>6</v>
+      </c>
+      <c r="V8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="s">
+        <v>57</v>
+      </c>
+      <c r="C9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" t="s">
+        <v>57</v>
+      </c>
+      <c r="E9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F9" t="s">
+        <v>58</v>
+      </c>
+      <c r="J9" t="s">
+        <v>57</v>
+      </c>
+      <c r="K9" t="s">
+        <v>20</v>
+      </c>
+      <c r="L9" t="s">
+        <v>80</v>
+      </c>
+      <c r="M9" t="s">
+        <v>81</v>
+      </c>
+      <c r="N9" t="s">
+        <v>81</v>
+      </c>
+      <c r="R9" t="s">
+        <v>57</v>
+      </c>
+      <c r="S9" t="s">
+        <v>12</v>
+      </c>
+      <c r="T9" t="s">
+        <v>22</v>
+      </c>
+      <c r="U9" t="s">
+        <v>12</v>
+      </c>
+      <c r="V9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="s">
+        <v>58</v>
+      </c>
+      <c r="C10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D10" t="s">
+        <v>60</v>
+      </c>
+      <c r="E10" t="s">
+        <v>15</v>
+      </c>
+      <c r="F10" t="s">
+        <v>70</v>
+      </c>
+      <c r="J10" t="s">
+        <v>58</v>
+      </c>
+      <c r="K10" t="s">
+        <v>15</v>
+      </c>
+      <c r="L10" t="s">
+        <v>82</v>
+      </c>
+      <c r="M10" t="s">
+        <v>81</v>
+      </c>
+      <c r="N10" t="s">
+        <v>81</v>
+      </c>
+      <c r="R10" t="s">
+        <v>58</v>
+      </c>
+      <c r="S10" t="s">
+        <v>20</v>
+      </c>
+      <c r="T10" t="s">
+        <v>15</v>
+      </c>
+      <c r="U10" t="s">
+        <v>26</v>
+      </c>
+      <c r="V10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/test/fixtures/xlsx/multi-target/multi-target.xlsx
+++ b/test/fixtures/xlsx/multi-target/multi-target.xlsx
@@ -14,38 +14,47 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="93">
-  <si>
-    <t xml:space="preserve">~~table:Weapon~~</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="95">
+  <si>
+    <t xml:space="preserve">:table Weapon</t>
   </si>
   <si>
     <t xml:space="preserve">first target of every column below</t>
   </si>
   <si>
+    <t xml:space="preserve">:field</t>
+  </si>
+  <si>
+    <t xml:space="preserve">:type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">:desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">:target</t>
+  </si>
+  <si>
     <t xml:space="preserve">index</t>
   </si>
   <si>
+    <t xml:space="preserve">int</t>
+  </si>
+  <si>
     <t xml:space="preserve">primary index, in this table's own band</t>
   </si>
   <si>
-    <t xml:space="preserve">int</t>
-  </si>
-  <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
     <t xml:space="preserve">cs</t>
   </si>
   <si>
     <t xml:space="preserve">Name</t>
   </si>
   <si>
+    <t xml:space="preserve">string</t>
+  </si>
+  <si>
     <t xml:space="preserve">so the resolved row has something to read</t>
   </si>
   <si>
-    <t xml:space="preserve">string</t>
-  </si>
-  <si>
     <t xml:space="preserve">Note</t>
   </si>
   <si>
@@ -70,7 +79,7 @@
     <t xml:space="preserve">b</t>
   </si>
   <si>
-    <t xml:space="preserve">~~table:Armour~~</t>
+    <t xml:space="preserve">:table Armour</t>
   </si>
   <si>
     <t xml:space="preserve">second target</t>
@@ -88,7 +97,7 @@
     <t xml:space="preserve">armour-b</t>
   </si>
   <si>
-    <t xml:space="preserve">~~table:Trinket~~</t>
+    <t xml:space="preserve">:table Trinket</t>
   </si>
   <si>
     <t xml:space="preserve">only the wide column names this</t>
@@ -106,7 +115,7 @@
     <t xml:space="preserve">trinket-b</t>
   </si>
   <si>
-    <t xml:space="preserve">~~table:Mount~~</t>
+    <t xml:space="preserve">:table Mount</t>
   </si>
   <si>
     <t xml:space="preserve">40</t>
@@ -121,7 +130,7 @@
     <t xml:space="preserve">mount-b</t>
   </si>
   <si>
-    <t xml:space="preserve">~~table:Banner~~</t>
+    <t xml:space="preserve">:table Banner</t>
   </si>
   <si>
     <t xml:space="preserve">the wide column's last target</t>
@@ -139,7 +148,7 @@
     <t xml:space="preserve">banner-b</t>
   </si>
   <si>
-    <t xml:space="preserve">~~table:Holder~~</t>
+    <t xml:space="preserve">:table Holder</t>
   </si>
   <si>
     <t xml:space="preserve">One column per case the spec states.</t>
@@ -151,42 +160,39 @@
     <t xml:space="preserve">Pick</t>
   </si>
   <si>
+    <t xml:space="preserve">foreign Weapon|Armour</t>
+  </si>
+  <si>
     <t xml:space="preserve">two targets - the ordinary case</t>
   </si>
   <si>
-    <t xml:space="preserve">foreign</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon|Armour</t>
-  </si>
-  <si>
     <t xml:space="preserve">Wide</t>
   </si>
   <si>
+    <t xml:space="preserve">foreign Weapon|Armour|Trinket|Mount|Banner</t>
+  </si>
+  <si>
     <t xml:space="preserve">five targets, and the value picks one</t>
   </si>
   <si>
-    <t xml:space="preserve">Weapon|Armour|Trinket|Mount|Banner</t>
-  </si>
-  <si>
     <t xml:space="preserve">Only</t>
   </si>
   <si>
+    <t xml:space="preserve">foreign Weapon</t>
+  </si>
+  <si>
     <t xml:space="preserve">the same notation with one name</t>
   </si>
   <si>
-    <t xml:space="preserve">Weapon</t>
-  </si>
-  <si>
     <t xml:space="preserve">Maybe</t>
   </si>
   <si>
+    <t xml:space="preserve">foreign Weapon|Armour?</t>
+  </si>
+  <si>
     <t xml:space="preserve">two targets, and `-` is none of them</t>
   </si>
   <si>
-    <t xml:space="preserve">foreign?</t>
-  </si>
-  <si>
     <t xml:space="preserve">1</t>
   </si>
   <si>
@@ -199,37 +205,37 @@
     <t xml:space="preserve">3</t>
   </si>
   <si>
-    <t xml:space="preserve">~~table:Loadout~~</t>
+    <t xml:space="preserve">:table Loadout</t>
   </si>
   <si>
     <t xml:space="preserve">A record array whose member reaches several tables.</t>
   </si>
   <si>
-    <t xml:space="preserve">Slot1.Pick</t>
+    <t xml:space="preserve">Slot[0].Pick</t>
   </si>
   <si>
     <t xml:space="preserve">element 1 - two targets</t>
   </si>
   <si>
-    <t xml:space="preserve">Slot1.Count</t>
+    <t xml:space="preserve">Slot[0].Count</t>
   </si>
   <si>
     <t xml:space="preserve">element 1 - an ordinary member</t>
   </si>
   <si>
-    <t xml:space="preserve">Slot2.Pick</t>
+    <t xml:space="preserve">Slot[1].Pick</t>
   </si>
   <si>
     <t xml:space="preserve">element 2</t>
   </si>
   <si>
-    <t xml:space="preserve">Slot2.Count</t>
+    <t xml:space="preserve">Slot[1].Count</t>
   </si>
   <si>
     <t xml:space="preserve">4</t>
   </si>
   <si>
-    <t xml:space="preserve">~~table:Fitting~~</t>
+    <t xml:space="preserve">:table Fitting</t>
   </si>
   <si>
     <t xml:space="preserve">One record - no element number at all - whose member reaches several.</t>
@@ -265,31 +271,31 @@
     <t xml:space="preserve">6</t>
   </si>
   <si>
-    <t xml:space="preserve">~~table:Rack~~</t>
+    <t xml:space="preserve">:table Rack</t>
   </si>
   <si>
     <t xml:space="preserve">One record whose members are arrays, one of them reaching several.</t>
   </si>
   <si>
-    <t xml:space="preserve">Slots.Pick1</t>
+    <t xml:space="preserve">Slots.Pick[0]</t>
   </si>
   <si>
     <t xml:space="preserve">element 1 of the member</t>
   </si>
   <si>
-    <t xml:space="preserve">Slots.Pick2</t>
+    <t xml:space="preserve">Slots.Pick[1]</t>
   </si>
   <si>
     <t xml:space="preserve">element 2 of the member</t>
   </si>
   <si>
-    <t xml:space="preserve">Slots.Count1</t>
+    <t xml:space="preserve">Slots.Count[0]</t>
   </si>
   <si>
     <t xml:space="preserve">element 1 beside it</t>
   </si>
   <si>
-    <t xml:space="preserve">Slots.Count2</t>
+    <t xml:space="preserve">Slots.Count[1]</t>
   </si>
   <si>
     <t xml:space="preserve">element 2 beside it</t>
@@ -337,140 +343,230 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="B2:AJ10"/>
+  <dimension ref="B2:AK8"/>
   <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
       <c r="B2" t="s">
         <v>0</v>
       </c>
+      <c r="C2" t="s">
+        <v>1</v>
+      </c>
       <c r="J2" t="s">
-        <v>18</v>
+        <v>21</v>
+      </c>
+      <c r="K2" t="s">
+        <v>22</v>
       </c>
       <c r="R2" t="s">
-        <v>24</v>
+        <v>27</v>
+      </c>
+      <c r="S2" t="s">
+        <v>28</v>
       </c>
       <c r="Z2" t="s">
-        <v>30</v>
+        <v>33</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>28</v>
       </c>
       <c r="AH2" t="s">
-        <v>35</v>
+        <v>38</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="3">
       <c r="B3" t="s">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" t="s">
+        <v>13</v>
       </c>
       <c r="J3" t="s">
-        <v>19</v>
+        <v>2</v>
+      </c>
+      <c r="K3" t="s">
+        <v>6</v>
+      </c>
+      <c r="L3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M3" t="s">
+        <v>13</v>
       </c>
       <c r="R3" t="s">
-        <v>25</v>
+        <v>2</v>
+      </c>
+      <c r="S3" t="s">
+        <v>6</v>
+      </c>
+      <c r="T3" t="s">
+        <v>10</v>
+      </c>
+      <c r="U3" t="s">
+        <v>13</v>
       </c>
       <c r="Z3" t="s">
-        <v>25</v>
+        <v>2</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>6</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>13</v>
       </c>
       <c r="AH3" t="s">
-        <v>36</v>
+        <v>2</v>
+      </c>
+      <c r="AI3" t="s">
+        <v>6</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AK3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" t="s">
         <v>7</v>
       </c>
       <c r="D4" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>11</v>
       </c>
       <c r="J4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K4" t="s">
         <v>7</v>
       </c>
       <c r="L4" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="M4" t="s">
+        <v>11</v>
       </c>
       <c r="R4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S4" t="s">
         <v>7</v>
       </c>
       <c r="T4" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="U4" t="s">
+        <v>11</v>
       </c>
       <c r="Z4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA4" t="s">
         <v>7</v>
       </c>
       <c r="AB4" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>11</v>
       </c>
       <c r="AH4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI4" t="s">
         <v>7</v>
       </c>
       <c r="AJ4" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="AK4" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C5" t="s">
         <v>8</v>
       </c>
       <c r="D5" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="E5" t="s">
+        <v>14</v>
       </c>
       <c r="J5" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K5" t="s">
         <v>8</v>
       </c>
       <c r="L5" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="M5" t="s">
+        <v>14</v>
       </c>
       <c r="R5" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S5" t="s">
         <v>8</v>
       </c>
       <c r="T5" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="U5" t="s">
+        <v>14</v>
       </c>
       <c r="Z5" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA5" t="s">
         <v>8</v>
       </c>
       <c r="AB5" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>14</v>
       </c>
       <c r="AH5" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI5" t="s">
         <v>8</v>
       </c>
       <c r="AJ5" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="AK5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C6" t="s">
         <v>9</v>
@@ -478,8 +574,11 @@
       <c r="D6" t="s">
         <v>9</v>
       </c>
+      <c r="E6" t="s">
+        <v>9</v>
+      </c>
       <c r="J6" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K6" t="s">
         <v>9</v>
@@ -487,8 +586,11 @@
       <c r="L6" t="s">
         <v>9</v>
       </c>
+      <c r="M6" t="s">
+        <v>9</v>
+      </c>
       <c r="R6" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S6" t="s">
         <v>9</v>
@@ -496,8 +598,11 @@
       <c r="T6" t="s">
         <v>9</v>
       </c>
+      <c r="U6" t="s">
+        <v>9</v>
+      </c>
       <c r="Z6" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA6" t="s">
         <v>9</v>
@@ -505,8 +610,11 @@
       <c r="AB6" t="s">
         <v>9</v>
       </c>
+      <c r="AC6" t="s">
+        <v>9</v>
+      </c>
       <c r="AH6" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI6" t="s">
         <v>9</v>
@@ -514,193 +622,102 @@
       <c r="AJ6" t="s">
         <v>9</v>
       </c>
+      <c r="AK6" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="7">
-      <c r="B7" t="s">
-        <v>5</v>
-      </c>
       <c r="C7" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D7" t="s">
-        <v>5</v>
-      </c>
-      <c r="J7" t="s">
-        <v>5</v>
+        <v>16</v>
+      </c>
+      <c r="E7" t="s">
+        <v>17</v>
       </c>
       <c r="K7" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="L7" t="s">
-        <v>5</v>
-      </c>
-      <c r="R7" t="s">
-        <v>5</v>
+        <v>24</v>
+      </c>
+      <c r="M7" t="s">
+        <v>17</v>
       </c>
       <c r="S7" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="T7" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z7" t="s">
-        <v>5</v>
+        <v>30</v>
+      </c>
+      <c r="U7" t="s">
+        <v>17</v>
       </c>
       <c r="AA7" t="s">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="AB7" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH7" t="s">
-        <v>5</v>
+        <v>35</v>
+      </c>
+      <c r="AC7" t="s">
+        <v>17</v>
       </c>
       <c r="AI7" t="s">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="AJ7" t="s">
-        <v>5</v>
+        <v>41</v>
+      </c>
+      <c r="AK7" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="8">
-      <c r="B8" t="s">
-        <v>6</v>
-      </c>
       <c r="C8" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="D8" t="s">
-        <v>6</v>
-      </c>
-      <c r="J8" t="s">
-        <v>6</v>
+        <v>19</v>
+      </c>
+      <c r="E8" t="s">
+        <v>20</v>
       </c>
       <c r="K8" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="L8" t="s">
-        <v>6</v>
-      </c>
-      <c r="R8" t="s">
-        <v>6</v>
+        <v>26</v>
+      </c>
+      <c r="M8" t="s">
+        <v>20</v>
       </c>
       <c r="S8" t="s">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="T8" t="s">
-        <v>6</v>
-      </c>
-      <c r="Z8" t="s">
-        <v>6</v>
+        <v>32</v>
+      </c>
+      <c r="U8" t="s">
+        <v>20</v>
       </c>
       <c r="AA8" t="s">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="AB8" t="s">
-        <v>6</v>
-      </c>
-      <c r="AH8" t="s">
-        <v>6</v>
+        <v>37</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>20</v>
       </c>
       <c r="AI8" t="s">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="AJ8" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D9" t="s">
-        <v>14</v>
-      </c>
-      <c r="J9" t="s">
+        <v>43</v>
+      </c>
+      <c r="AK8" t="s">
         <v>20</v>
-      </c>
-      <c r="K9" t="s">
-        <v>21</v>
-      </c>
-      <c r="L9" t="s">
-        <v>14</v>
-      </c>
-      <c r="R9" t="s">
-        <v>26</v>
-      </c>
-      <c r="S9" t="s">
-        <v>27</v>
-      </c>
-      <c r="T9" t="s">
-        <v>14</v>
-      </c>
-      <c r="Z9" t="s">
-        <v>31</v>
-      </c>
-      <c r="AA9" t="s">
-        <v>32</v>
-      </c>
-      <c r="AB9" t="s">
-        <v>14</v>
-      </c>
-      <c r="AH9" t="s">
-        <v>37</v>
-      </c>
-      <c r="AI9" t="s">
-        <v>38</v>
-      </c>
-      <c r="AJ9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10" t="s">
-        <v>16</v>
-      </c>
-      <c r="D10" t="s">
-        <v>17</v>
-      </c>
-      <c r="J10" t="s">
-        <v>22</v>
-      </c>
-      <c r="K10" t="s">
-        <v>23</v>
-      </c>
-      <c r="L10" t="s">
-        <v>17</v>
-      </c>
-      <c r="R10" t="s">
-        <v>28</v>
-      </c>
-      <c r="S10" t="s">
-        <v>29</v>
-      </c>
-      <c r="T10" t="s">
-        <v>17</v>
-      </c>
-      <c r="Z10" t="s">
-        <v>33</v>
-      </c>
-      <c r="AA10" t="s">
-        <v>34</v>
-      </c>
-      <c r="AB10" t="s">
-        <v>17</v>
-      </c>
-      <c r="AH10" t="s">
-        <v>39</v>
-      </c>
-      <c r="AI10" t="s">
-        <v>40</v>
-      </c>
-      <c r="AJ10" t="s">
-        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -710,25 +727,43 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="B2:F11"/>
+  <dimension ref="B2:G9"/>
   <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
       <c r="B2" t="s">
-        <v>41</v>
+        <v>44</v>
+      </c>
+      <c r="C2" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="3">
       <c r="B3" t="s">
-        <v>42</v>
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F3" t="s">
+        <v>53</v>
+      </c>
+      <c r="G3" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="D4" t="s">
         <v>48</v>
@@ -739,13 +774,16 @@
       <c r="F4" t="s">
         <v>54</v>
       </c>
+      <c r="G4" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="5">
       <c r="B5" t="s">
-        <v>43</v>
+        <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D5" t="s">
         <v>49</v>
@@ -756,107 +794,79 @@
       <c r="F5" t="s">
         <v>55</v>
       </c>
+      <c r="G5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="6">
       <c r="B6" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>46</v>
+        <v>9</v>
       </c>
       <c r="D6" t="s">
-        <v>46</v>
+        <v>9</v>
       </c>
       <c r="E6" t="s">
-        <v>46</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>56</v>
+        <v>9</v>
+      </c>
+      <c r="G6" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="7">
-      <c r="B7" t="s">
-        <v>5</v>
-      </c>
       <c r="C7" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="D7" t="s">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="E7" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="F7" t="s">
-        <v>47</v>
+        <v>15</v>
+      </c>
+      <c r="G7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="8">
-      <c r="B8" t="s">
-        <v>6</v>
-      </c>
       <c r="C8" t="s">
-        <v>6</v>
+        <v>60</v>
       </c>
       <c r="D8" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="E8" t="s">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="F8" t="s">
-        <v>6</v>
+        <v>18</v>
+      </c>
+      <c r="G8" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="9">
-      <c r="B9" t="s">
-        <v>57</v>
-      </c>
       <c r="C9" t="s">
-        <v>12</v>
+        <v>62</v>
       </c>
       <c r="D9" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="E9" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F9" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" t="s">
-        <v>58</v>
-      </c>
-      <c r="C10" t="s">
-        <v>22</v>
-      </c>
-      <c r="D10" t="s">
-        <v>39</v>
-      </c>
-      <c r="E10" t="s">
         <v>15</v>
       </c>
-      <c r="F10" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" t="s">
-        <v>60</v>
-      </c>
-      <c r="C11" t="s">
-        <v>15</v>
-      </c>
-      <c r="D11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E11" t="s">
-        <v>12</v>
-      </c>
-      <c r="F11" t="s">
-        <v>22</v>
+      <c r="G9" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -866,84 +876,147 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="B2:V10"/>
+  <dimension ref="B2:W8"/>
   <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
       <c r="B2" t="s">
-        <v>61</v>
+        <v>63</v>
+      </c>
+      <c r="C2" t="s">
+        <v>64</v>
       </c>
       <c r="J2" t="s">
-        <v>71</v>
+        <v>73</v>
+      </c>
+      <c r="K2" t="s">
+        <v>74</v>
       </c>
       <c r="R2" t="s">
-        <v>83</v>
+        <v>85</v>
+      </c>
+      <c r="S2" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="3">
       <c r="B3" t="s">
-        <v>62</v>
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" t="s">
+        <v>65</v>
+      </c>
+      <c r="E3" t="s">
+        <v>67</v>
+      </c>
+      <c r="F3" t="s">
+        <v>69</v>
+      </c>
+      <c r="G3" t="s">
+        <v>71</v>
       </c>
       <c r="J3" t="s">
-        <v>72</v>
+        <v>2</v>
+      </c>
+      <c r="K3" t="s">
+        <v>6</v>
+      </c>
+      <c r="L3" t="s">
+        <v>75</v>
+      </c>
+      <c r="M3" t="s">
+        <v>77</v>
+      </c>
+      <c r="N3" t="s">
+        <v>79</v>
+      </c>
+      <c r="O3" t="s">
+        <v>81</v>
       </c>
       <c r="R3" t="s">
-        <v>84</v>
+        <v>2</v>
+      </c>
+      <c r="S3" t="s">
+        <v>6</v>
+      </c>
+      <c r="T3" t="s">
+        <v>87</v>
+      </c>
+      <c r="U3" t="s">
+        <v>89</v>
+      </c>
+      <c r="V3" t="s">
+        <v>91</v>
+      </c>
+      <c r="W3" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>63</v>
+        <v>7</v>
       </c>
       <c r="D4" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="E4" t="s">
-        <v>67</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>69</v>
+        <v>48</v>
+      </c>
+      <c r="G4" t="s">
+        <v>7</v>
       </c>
       <c r="J4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K4" t="s">
-        <v>73</v>
+        <v>7</v>
       </c>
       <c r="L4" t="s">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="M4" t="s">
-        <v>77</v>
+        <v>7</v>
       </c>
       <c r="N4" t="s">
-        <v>79</v>
+        <v>7</v>
+      </c>
+      <c r="O4" t="s">
+        <v>7</v>
       </c>
       <c r="R4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S4" t="s">
-        <v>85</v>
+        <v>7</v>
       </c>
       <c r="T4" t="s">
-        <v>87</v>
+        <v>48</v>
       </c>
       <c r="U4" t="s">
-        <v>89</v>
+        <v>48</v>
       </c>
       <c r="V4" t="s">
-        <v>91</v>
+        <v>7</v>
+      </c>
+      <c r="W4" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" t="s">
-        <v>43</v>
+        <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="D5" t="s">
         <v>66</v>
@@ -952,13 +1025,16 @@
         <v>68</v>
       </c>
       <c r="F5" t="s">
-        <v>68</v>
+        <v>70</v>
+      </c>
+      <c r="G5" t="s">
+        <v>70</v>
       </c>
       <c r="J5" t="s">
-        <v>43</v>
+        <v>4</v>
       </c>
       <c r="K5" t="s">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="L5" t="s">
         <v>76</v>
@@ -967,13 +1043,16 @@
         <v>78</v>
       </c>
       <c r="N5" t="s">
-        <v>78</v>
+        <v>80</v>
+      </c>
+      <c r="O5" t="s">
+        <v>80</v>
       </c>
       <c r="R5" t="s">
-        <v>43</v>
+        <v>4</v>
       </c>
       <c r="S5" t="s">
-        <v>86</v>
+        <v>46</v>
       </c>
       <c r="T5" t="s">
         <v>88</v>
@@ -984,240 +1063,158 @@
       <c r="V5" t="s">
         <v>92</v>
       </c>
+      <c r="W5" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="6">
       <c r="B6" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>46</v>
+        <v>9</v>
       </c>
       <c r="D6" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E6" t="s">
-        <v>46</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>4</v>
+        <v>9</v>
+      </c>
+      <c r="G6" t="s">
+        <v>9</v>
       </c>
       <c r="J6" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K6" t="s">
-        <v>46</v>
+        <v>9</v>
       </c>
       <c r="L6" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="M6" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="N6" t="s">
-        <v>4</v>
+        <v>9</v>
+      </c>
+      <c r="O6" t="s">
+        <v>9</v>
       </c>
       <c r="R6" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S6" t="s">
-        <v>46</v>
+        <v>9</v>
       </c>
       <c r="T6" t="s">
-        <v>46</v>
+        <v>9</v>
       </c>
       <c r="U6" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="V6" t="s">
-        <v>4</v>
+        <v>9</v>
+      </c>
+      <c r="W6" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="7">
-      <c r="B7" t="s">
-        <v>5</v>
-      </c>
       <c r="C7" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="D7" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E7" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="F7" t="s">
-        <v>5</v>
-      </c>
-      <c r="J7" t="s">
-        <v>5</v>
+        <v>23</v>
+      </c>
+      <c r="G7" t="s">
+        <v>60</v>
       </c>
       <c r="K7" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="L7" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="M7" t="s">
-        <v>5</v>
+        <v>82</v>
       </c>
       <c r="N7" t="s">
-        <v>5</v>
-      </c>
-      <c r="R7" t="s">
-        <v>5</v>
+        <v>83</v>
+      </c>
+      <c r="O7" t="s">
+        <v>83</v>
       </c>
       <c r="S7" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="T7" t="s">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="U7" t="s">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="V7" t="s">
-        <v>5</v>
+        <v>15</v>
+      </c>
+      <c r="W7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="8">
-      <c r="B8" t="s">
-        <v>6</v>
-      </c>
       <c r="C8" t="s">
-        <v>6</v>
+        <v>60</v>
       </c>
       <c r="D8" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="E8" t="s">
-        <v>6</v>
+        <v>62</v>
       </c>
       <c r="F8" t="s">
-        <v>6</v>
-      </c>
-      <c r="J8" t="s">
-        <v>6</v>
+        <v>18</v>
+      </c>
+      <c r="G8" t="s">
+        <v>72</v>
       </c>
       <c r="K8" t="s">
-        <v>6</v>
+        <v>60</v>
       </c>
       <c r="L8" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="M8" t="s">
-        <v>6</v>
+        <v>84</v>
       </c>
       <c r="N8" t="s">
-        <v>6</v>
-      </c>
-      <c r="R8" t="s">
-        <v>6</v>
+        <v>83</v>
+      </c>
+      <c r="O8" t="s">
+        <v>83</v>
       </c>
       <c r="S8" t="s">
-        <v>6</v>
+        <v>60</v>
       </c>
       <c r="T8" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="U8" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="V8" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" t="s">
-        <v>57</v>
-      </c>
-      <c r="C9" t="s">
-        <v>12</v>
-      </c>
-      <c r="D9" t="s">
-        <v>57</v>
-      </c>
-      <c r="E9" t="s">
-        <v>20</v>
-      </c>
-      <c r="F9" t="s">
-        <v>58</v>
-      </c>
-      <c r="J9" t="s">
-        <v>57</v>
-      </c>
-      <c r="K9" t="s">
-        <v>20</v>
-      </c>
-      <c r="L9" t="s">
-        <v>80</v>
-      </c>
-      <c r="M9" t="s">
-        <v>81</v>
-      </c>
-      <c r="N9" t="s">
-        <v>81</v>
-      </c>
-      <c r="R9" t="s">
-        <v>57</v>
-      </c>
-      <c r="S9" t="s">
-        <v>12</v>
-      </c>
-      <c r="T9" t="s">
-        <v>22</v>
-      </c>
-      <c r="U9" t="s">
-        <v>12</v>
-      </c>
-      <c r="V9" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" t="s">
-        <v>58</v>
-      </c>
-      <c r="C10" t="s">
-        <v>22</v>
-      </c>
-      <c r="D10" t="s">
-        <v>60</v>
-      </c>
-      <c r="E10" t="s">
-        <v>15</v>
-      </c>
-      <c r="F10" t="s">
-        <v>70</v>
-      </c>
-      <c r="J10" t="s">
-        <v>58</v>
-      </c>
-      <c r="K10" t="s">
-        <v>15</v>
-      </c>
-      <c r="L10" t="s">
-        <v>82</v>
-      </c>
-      <c r="M10" t="s">
-        <v>81</v>
-      </c>
-      <c r="N10" t="s">
-        <v>81</v>
-      </c>
-      <c r="R10" t="s">
-        <v>58</v>
-      </c>
-      <c r="S10" t="s">
-        <v>20</v>
-      </c>
-      <c r="T10" t="s">
-        <v>15</v>
-      </c>
-      <c r="U10" t="s">
-        <v>26</v>
-      </c>
-      <c r="V10" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="W8" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
